--- a/public/decision-log-template.xlsx
+++ b/public/decision-log-template.xlsx
@@ -620,6 +620,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I501">
+      <formula1>"Proposed,Live,Superseded,Reversed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
